--- a/Data/China_GNSS.xlsx
+++ b/Data/China_GNSS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10720"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://csiroau-my.sharepoint.com/personal/lin253_csiro_au/Documents/China Coastline/Manuscript/China_database_YC_LIN/Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://csiroau-my.sharepoint.com/personal/lin253_csiro_au/Documents/China Coastline/Manuscript/Submission 3/China_database_YC_LIN_v3/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{F4CBCE87-AD7B-D349-AB4B-251C30D0E889}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA7C14F5-5805-BF4C-A000-3D53BC24EEE8}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{F4CBCE87-AD7B-D349-AB4B-251C30D0E889}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56A94295-27C6-E44E-A783-C4F868B5F547}"/>
   <bookViews>
-    <workbookView xWindow="34560" yWindow="3720" windowWidth="51200" windowHeight="28300" activeTab="1" xr2:uid="{AA3C8630-698E-5740-B3D6-CAA2451465C3}"/>
+    <workbookView xWindow="30240" yWindow="500" windowWidth="51200" windowHeight="28300" activeTab="1" xr2:uid="{AA3C8630-698E-5740-B3D6-CAA2451465C3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Data/China_GNSS.xlsx
+++ b/Data/China_GNSS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10720"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://csiroau-my.sharepoint.com/personal/lin253_csiro_au/Documents/China Coastline/Manuscript/Submission 3/China_database_YC_LIN_v3/Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lin253/Downloads/Manuscript/Manuscript/Submission 3/China_database_YC_LIN_v3/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{F4CBCE87-AD7B-D349-AB4B-251C30D0E889}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56A94295-27C6-E44E-A783-C4F868B5F547}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{374AE32B-9E30-EA41-B01D-6C86F7C918C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30240" yWindow="500" windowWidth="51200" windowHeight="28300" activeTab="1" xr2:uid="{AA3C8630-698E-5740-B3D6-CAA2451465C3}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>Station name</t>
   </si>
@@ -139,6 +139,9 @@
   </si>
   <si>
     <t>The database comprise China GNSS data obtained from Nevada Geodetic Laboratory at the University of Nevada http://geodesy.unr.edu. Last access: 10/Oct/2024.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    </t>
   </si>
 </sst>
 </file>
@@ -1221,6 +1224,11 @@
         <v>31</v>
       </c>
     </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>34</v>
+      </c>
+    </row>
     <row r="6" spans="1:1" ht="40" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>33</v>
